--- a/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_09-Finishes_ABCTile_pending.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_09-Finishes_ABCTile_pending.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Row 2 = section total (sets CSI division). Line items follow. Pre-Tax Total row has empty Description so grand_total is captured.</t>
+          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Only QI-* rows are real quote line items. Row 2 (Item_ID empty) is a parser-control section-total row that sets the current CSI division for all QI-* rows that follow. The final row (Item_ID='Pre-Tax Total', Description empty) is a parser-control row that the grid parser captures as grand_total, not a line item.</t>
         </is>
       </c>
     </row>

--- a/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_09-Finishes_ABCTile_pending.xlsx
+++ b/docs/templates/mock_drive/2026001 — Rockland/quotes/2026001_QUOTE_09-Finishes_ABCTile_pending.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,6 +501,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SOW_Item_Ref</t>
         </is>
       </c>
     </row>
@@ -524,6 +530,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,6 +571,11 @@
           <t>12x24 porcelain; incl. waterproofing</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SOW-040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -604,6 +616,11 @@
           <t>5/8" Type X</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SOW-041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,6 +661,11 @@
           <t>Lifeproof 6mm</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SOW-042</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -682,6 +704,11 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>BM Chantilly Lace</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SOW-043</t>
         </is>
       </c>
     </row>
@@ -702,6 +729,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -774,7 +802,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Only QI-* rows are real quote line items. Row 2 (Item_ID empty) is a parser-control section-total row that sets the current CSI division for all QI-* rows that follow. The final row (Item_ID='Pre-Tax Total', Description empty) is a parser-control row that the grid parser captures as grand_total, not a line item.</t>
+          <t>Subcontractor quote. Grid-readable: Material Amount / Labour Amount / Total Amount. Only QI-* rows are real quote line items. Row 2 (Item_ID empty) is a parser-control section-total row that sets the current CSI division for all QI-* rows that follow. The final row (Item_ID='Pre-Tax Total', Description empty) is a parser-control row that the grid parser captures as grand_total, not a line item. SOW_Item_Ref is the structural join key back to SOW_Items/Package_Lines (e.g. 'SOW-025') -- never parse it out of Notes text.</t>
         </is>
       </c>
     </row>
